--- a/Tableau Synthèse.xlsx
+++ b/Tableau Synthèse.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\betan\OneDrive\Bureau\PHOTO\Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\betan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC38806D-7750-4404-BE18-7D47B0166EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC076DCB-C9B8-4DA0-8B51-56F30E011F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="49">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -86,9 +86,6 @@
 ▸Développer son projet professionnel</t>
   </si>
   <si>
-    <t>Centre de formation :</t>
-  </si>
-  <si>
     <t>▢ SLAM</t>
   </si>
   <si>
@@ -104,9 +101,6 @@
     <t xml:space="preserve">N° candidat : </t>
   </si>
   <si>
-    <t xml:space="preserve">NOM et prénom : </t>
-  </si>
-  <si>
     <t>Période (sous la forme du JJ/MM/AA au JJ/MM/AA)</t>
   </si>
   <si>
@@ -125,13 +119,6 @@
     <t>x SISR</t>
   </si>
   <si>
-    <t xml:space="preserve">
-</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gestion des tickets GLPI </t>
   </si>
   <si>
@@ -145,6 +132,63 @@
   </si>
   <si>
     <t>Procédure explicative pour résoudre un problème</t>
+  </si>
+  <si>
+    <t>Serveur AD</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Gestion Tickets (GLPI)</t>
+  </si>
+  <si>
+    <t>Virtualisation (vmware)</t>
+  </si>
+  <si>
+    <t>Securisation serveur (ssh/ / pare feu/ fail to ban)</t>
+  </si>
+  <si>
+    <t>Création /hébergement d'un site (portfolio via git-hub)</t>
+  </si>
+  <si>
+    <t>Commutation d'un réseau (InterVLANS)</t>
+  </si>
+  <si>
+    <t>Pare-feu (pf-sense)</t>
+  </si>
+  <si>
+    <t>Routage dynamique RIP et OSPF</t>
+  </si>
+  <si>
+    <t>Filtrage du réseau via des ACLs (access list)</t>
+  </si>
+  <si>
+    <t>Assurer une haute disponibilité via HSRP</t>
+  </si>
+  <si>
+    <t>Maintenance du materiel informatique</t>
+  </si>
+  <si>
+    <t>Déploiement Windows 11 et intégration domaine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crétion de documentations et tuoriels techniques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesion du stock et des ressources matérielles </t>
+  </si>
+  <si>
+    <t>Cartographie et documentation de l’infrastructure réseau</t>
+  </si>
+  <si>
+    <t>Centre de formation : ORT Daniel Mayer Montreuil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOM et prénom BETANCOURT Brandon </t>
+  </si>
+  <si>
+    <t>Intervention technique à distance ou sur site</t>
   </si>
 </sst>
 </file>
@@ -154,7 +198,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -212,17 +256,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="16"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="22"/>
       <name val="Arial"/>
@@ -237,7 +270,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -639,28 +672,101 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF494529"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF494529"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
+        <color rgb="FF494529"/>
       </left>
       <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
+        <color rgb="FF494529"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF494529"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF494529"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF494529"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF494529"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF494529"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF494529"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF494529"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF494529"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF494529"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF494529"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF494529"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF494529"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
+        <color rgb="FF494529"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
       <right style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
+        <color indexed="64"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -669,7 +775,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -716,9 +822,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -734,15 +837,63 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -776,73 +927,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1164,84 +1276,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="24"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:43" ht="41" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="43"/>
+      <c r="A3" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="31"/>
+      <c r="H3" s="37"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="41"/>
+      <c r="A4" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="35"/>
       <c r="F4" s="14" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>16</v>
+        <v>24</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="35"/>
+      <c r="A5" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="50"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>21</v>
+      <c r="A6" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>19</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>0</v>
@@ -1263,8 +1375,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23"/>
-      <c r="B7" s="32"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="47"/>
       <c r="C7" s="8" t="s">
         <v>9</v>
       </c>
@@ -1320,16 +1432,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="27"/>
+      <c r="A8" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="42"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1367,14 +1479,20 @@
       <c r="AQ8"/>
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="18"/>
+      <c r="A9" s="56" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="51"/>
+      <c r="C9" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="54"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1412,14 +1530,20 @@
       <c r="AQ9"/>
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="18"/>
+      <c r="A10" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="51"/>
+      <c r="C10" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="54"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1457,14 +1581,18 @@
       <c r="AQ10"/>
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="18"/>
+      <c r="A11" s="57" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="51"/>
+      <c r="C11" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="54"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1502,14 +1630,20 @@
       <c r="AQ11"/>
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18"/>
+      <c r="A12" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="51"/>
+      <c r="C12" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="55"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1547,16 +1681,22 @@
       <c r="AQ12"/>
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="84.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="18"/>
+      <c r="A13" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="51"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="53"/>
+      <c r="H13" s="55" t="s">
+        <v>31</v>
+      </c>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1594,14 +1734,18 @@
       <c r="AQ13"/>
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="11"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="18"/>
+      <c r="A14" s="57" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="51"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="54"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1639,14 +1783,18 @@
       <c r="AQ14"/>
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="18"/>
+      <c r="A15" s="57" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="51"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="54"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1684,14 +1832,18 @@
       <c r="AQ15"/>
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="11"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="18"/>
+      <c r="A16" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="51"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="54"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1729,14 +1881,18 @@
       <c r="AQ16"/>
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="18"/>
+      <c r="A17" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="51"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="54"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1774,14 +1930,18 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="11"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="18"/>
+      <c r="A18" s="57" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="51"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="54"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1819,16 +1979,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="30"/>
+      <c r="A19" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="44"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="45"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1866,22 +2026,22 @@
       <c r="AQ19"/>
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="44" t="s">
-        <v>29</v>
+      <c r="A20" s="21" t="s">
+        <v>25</v>
       </c>
       <c r="B20" s="10"/>
-      <c r="C20" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" s="18"/>
+      <c r="C20" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="17"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -1919,24 +2079,24 @@
       <c r="AQ20"/>
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="46" t="s">
-        <v>30</v>
+      <c r="A21" s="22" t="s">
+        <v>26</v>
       </c>
       <c r="B21" s="10"/>
-      <c r="C21" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="17"/>
-      <c r="F21" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="G21" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="H21" s="47"/>
+      <c r="C21" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="16"/>
+      <c r="F21" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="G21" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="23"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -1974,24 +2134,24 @@
       <c r="AQ21"/>
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="44" t="s">
-        <v>31</v>
+      <c r="A22" s="21" t="s">
+        <v>27</v>
       </c>
       <c r="B22" s="10"/>
-      <c r="C22" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="E22" s="17"/>
-      <c r="F22" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="G22" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="H22" s="18"/>
+      <c r="C22" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="16"/>
+      <c r="F22" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="17"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -2029,22 +2189,22 @@
       <c r="AQ22"/>
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="44" t="s">
-        <v>32</v>
+      <c r="A23" s="21" t="s">
+        <v>28</v>
       </c>
       <c r="B23" s="10"/>
-      <c r="C23" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="H23" s="18"/>
+      <c r="C23" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" s="17"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -2082,22 +2242,22 @@
       <c r="AQ23"/>
     </row>
     <row r="24" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="44" t="s">
+      <c r="A24" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="48"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="G24" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="H24" s="51"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" s="26"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2135,19 +2295,19 @@
       <c r="AQ24"/>
     </row>
     <row r="25" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="46" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="55"/>
-      <c r="C25" s="56"/>
-      <c r="D25" s="57" t="s">
-        <v>28</v>
-      </c>
-      <c r="E25" s="56"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="58" t="s">
-        <v>28</v>
+      <c r="A25" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="27"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="60" t="s">
+        <v>31</v>
       </c>
       <c r="I25"/>
       <c r="J25"/>
@@ -2186,14 +2346,20 @@
       <c r="AQ25"/>
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="11"/>
-      <c r="B26" s="52"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
+      <c r="A26" s="57" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="51"/>
+      <c r="C26" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" s="52" t="s">
+        <v>31</v>
+      </c>
       <c r="E26" s="53"/>
       <c r="F26" s="53"/>
       <c r="G26" s="53"/>
-      <c r="H26" s="54"/>
+      <c r="H26" s="59"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2231,16 +2397,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A27" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="30"/>
+      <c r="A27" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="44"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="45"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2278,14 +2444,20 @@
       <c r="AQ27"/>
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="11"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="18"/>
+      <c r="A28" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="51"/>
+      <c r="C28" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28" s="54"/>
       <c r="I28"/>
       <c r="J28"/>
       <c r="K28"/>
@@ -2323,14 +2495,18 @@
       <c r="AQ28"/>
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="11"/>
+      <c r="A29" s="21" t="s">
+        <v>43</v>
+      </c>
       <c r="B29" s="10"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="18"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29" s="17"/>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
@@ -2368,14 +2544,20 @@
       <c r="AQ29"/>
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="11"/>
+      <c r="A30" s="21" t="s">
+        <v>44</v>
+      </c>
       <c r="B30" s="10"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="18"/>
+      <c r="C30" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="H30" s="17"/>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
@@ -2413,14 +2595,20 @@
       <c r="AQ30"/>
     </row>
     <row r="31" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="11"/>
+      <c r="A31" s="22" t="s">
+        <v>45</v>
+      </c>
       <c r="B31" s="10"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="18"/>
+      <c r="C31" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="G31" s="16"/>
+      <c r="H31" s="17"/>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
@@ -2458,14 +2646,22 @@
       <c r="AQ31"/>
     </row>
     <row r="32" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="11"/>
+      <c r="A32" s="22" t="s">
+        <v>48</v>
+      </c>
       <c r="B32" s="10"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="18"/>
+      <c r="C32" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="H32" s="17"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
@@ -2505,12 +2701,12 @@
     <row r="33" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="10"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="18"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="17"/>
       <c r="I33"/>
       <c r="J33"/>
       <c r="K33"/>
@@ -2550,12 +2746,12 @@
     <row r="34" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="12"/>
       <c r="B34" s="13"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="20"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="19"/>
       <c r="I34"/>
       <c r="J34"/>
       <c r="K34"/>
@@ -2685,11 +2881,6 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2697,6 +2888,11 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
